--- a/光伏配储项目/电价数据/2026/普宁站.xlsx
+++ b/光伏配储项目/电价数据/2026/普宁站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.34517</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.85517</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26551</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07834999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.28547</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.53891</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25741</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.09551</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.58408</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6157699999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7687999999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.22794</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.67188</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44307</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.68757</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9578300000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53742</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.29106</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.4102</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.1669</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.22353</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.40848</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.5325</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.76067</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.81872</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.28732</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.14005</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9473400000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.84404</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.80403</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.53903</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48711</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.44226</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7478899999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9328500000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.00156</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51403</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.53234</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50334</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48374</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47525</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.49142</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.50114</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6870299999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.65249</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8559500000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.46832</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7272799999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53039</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.67604</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.96001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62164</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.79592</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8528600000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.25244</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.69969</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.21121</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9081</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.3103</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.19517</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.38012</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10873</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.17979</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69867</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.05766</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9446599999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05798</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9340900000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.15915</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.94528</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.90159</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.94011</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45499</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33554</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52351</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50145</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45684</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43957</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48814</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45184</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.13701</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.09419</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.70547</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.69204</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.88546</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.8807999999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.8706900000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.87401</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.55846</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.8714</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.87185</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8746499999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.02315</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.60694</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81636</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.82298</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6940499999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.73227</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.84149</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45659</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5161699999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52549</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5999500000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.64654</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.64823</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6608099999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32285</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63005</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69908</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47195</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.64077</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.78947</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7796000000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.46661</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6565</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45325</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.53642</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.62863</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.81128</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.58399</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9324600000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.74702</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.62334</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5724400000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71409</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44267</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46217</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34305</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.54018</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45596</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46619</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.64135</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.72482</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42232</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.63024</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.54213</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.45572</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.50048</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.66952</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.46237</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.4709100000000001</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.49264</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5870299999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6921799999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65906</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5456</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.51532</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5026499999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.44472</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3328</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14246</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02164</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26314</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24882</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.07842</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31472</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.22587</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18104</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.15016</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24086</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16878</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24218</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20597</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18311</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16318</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24252</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19078</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26351</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10024</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00974</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20568</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19961</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00728</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05983</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05803</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31431</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.35747</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78626</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87025</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.64922</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5704900000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44876</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.56014</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6094700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.90786</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47729</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.59978</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85165</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60709</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.45609</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.16934</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25811</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32131</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93245</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.5136799999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5129400000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.21185</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.21144</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.45534</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.30418</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.23144</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.87849</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.61465</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.22181</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72905</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8574700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6790499999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.21929</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.22188</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.46464</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.47777</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43137</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47787</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.16424</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26407</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15379</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01582</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.27008</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.45308</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5862200000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.26633</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.25562</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.15855</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18396</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.17663</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17723</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17398</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14624</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23678</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.14946</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.14855</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.18716</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.17215</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.20144</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.18794</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.17346</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.24354</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.14636</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.20643</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26637</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27603</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27566</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24187</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27625</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2840299999999999</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.46734</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46944</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30175</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.42062</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.24095</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.72799</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5210199999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48333</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5302899999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.59829</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7631699999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47677</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.45381</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5851900000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.46967</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45866</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68121</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.44237</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49973</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44809</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7177100000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.24901</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19767</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27386</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.18673</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.17944</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26992</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18112</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.17859</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.13973</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22828</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.17832</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18412</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.21298</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19019</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.15181</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14381</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20491</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25194</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27716</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.24651</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26654</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26656</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22397</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20668</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.15735</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22502</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31734</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.04718</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26758</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27551</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27875</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26731</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64906</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.54557</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19106</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.2928</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48907</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68498</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6395700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6892999999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84688</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.51697</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.46386</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3105</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.28677</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4648</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.50483</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.54979</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5701900000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67564</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8600399999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.5522</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7779700000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61691</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64023</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30413</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.25166</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.03184</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26722</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.48339</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.21718</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.21914</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21482</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.26282</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.17231</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.16747</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.18468</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17697</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.20968</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17946</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21894</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20734</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.03543</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25397</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.03697</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.03615</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.15177</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18782</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.15054</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.03559</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.14187</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.14605</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.18387</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.14388</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.14892</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.03546</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.15144</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.0355</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.16154</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17048</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.13489</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26769</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.26333</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.59903</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26212</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00304</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27943</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24083</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26225</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.26824</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26216</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20633</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.23248</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.21342</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24853</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24434</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.16263</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.16953</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24854</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.15245</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.15431</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22954</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22096</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27666</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17276</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16995</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.04122</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19293</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21526</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20646</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.03897</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.03908</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.03908</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.03901</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18748</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.03908</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.03908</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16437</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.03858</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.03103</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24204</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.007990000000000001</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.009390000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15413</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01444</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00222</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03637</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01283</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03548</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20644</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.03846</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26244</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.03164</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.26612</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26975</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27031</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.15309</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.14895</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15306</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15063</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14694</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.13665</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.03719</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.03663</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.0358</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26949</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22177</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.26103</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85563</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8627100000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5859500000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00272</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00194</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06962</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.67941</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5399299999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.8308300000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00992</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.62959</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8557899999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.85402</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.85866</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9640700000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.42441</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30187</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48004</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25777</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25295</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.17364</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25128</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24514</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23892</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20424</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23596</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18961</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15149</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18541</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.14639</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.1489</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.13846</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.16521</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.2179</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22878</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24574</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25871</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28464</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28584</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.60354</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.15074</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8644500000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.8704299999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55921</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.71687</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.91296</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.60138</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19671</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31221</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.54948</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5633400000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.24234</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.90101</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.59893</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.79743</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.62967</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.55563</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.76902</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.70689</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.18066</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7621</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6211599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31684</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26315</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.53723</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.50469</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.52737</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.60482</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32049</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.74839</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47275</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26566</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.48849</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.45623</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5476599999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33469</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17616</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14581</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19874</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14727</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04832</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12203</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22669</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14286</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14587</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18699</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16023</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16968</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20351</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.17002</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.52778</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44758</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.48242</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.4556</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43353</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36612</v>
       </c>
     </row>
   </sheetData>
